--- a/data/trans_dic/IP44C$recibos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,68</t>
+          <t>3,22; 12,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,13</t>
+          <t>1,72; 8,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,57</t>
+          <t>3,08; 8,57</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 13,15</t>
+          <t>4,1; 14,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 12,87</t>
+          <t>2,85; 12,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,71</t>
+          <t>4,06; 10,54</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,26</t>
+          <t>1,56; 13,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 11,63</t>
+          <t>1,4; 11,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,22</t>
+          <t>2,41; 10,07</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,3</t>
+          <t>3,98; 10,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,71</t>
+          <t>3,99; 10,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,16</t>
+          <t>4,62; 9,22</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,27; 21,42</t>
+          <t>10,77; 21,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,84; 23,42</t>
+          <t>11,55; 22,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,68</t>
+          <t>12,36; 20,53</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 19,38</t>
+          <t>6,89; 19,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 25,56</t>
+          <t>9,18; 26,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,44; 20,0</t>
+          <t>9,74; 20,28</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,27</t>
+          <t>6,9; 11,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 10,94</t>
+          <t>7,23; 11,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 10,42</t>
+          <t>7,71; 10,52</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7184</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12576</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3309; 12420</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2308; 11116</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7281; 20298</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7212</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13399</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3880; 13324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2728; 11647</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7725; 20059</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2995</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>812; 7158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>896; 7255</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2791; 11657</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>14618</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13850</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28469</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>8538; 22589</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8484; 21580</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19727; 39376</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>17896</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26596</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44493</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12339; 24449</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18126; 35502</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33553; 55718</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>8072</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11252</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19324</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4579; 12962</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6323; 18243</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>13176; 27445</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>58120</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>66273</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>124393</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>44492; 71342</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>52911; 81819</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>106080; 144737</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$recibos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 12,07</t>
+          <t>3,51; 13,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,31</t>
+          <t>1,7; 8,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,57</t>
+          <t>3,22; 8,53</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 14,07</t>
+          <t>4,03; 13,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,19</t>
+          <t>3,04; 12,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 10,54</t>
+          <t>4,21; 11,16</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,8</t>
+          <t>1,75; 14,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,36</t>
+          <t>1,25; 11,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 10,07</t>
+          <t>2,57; 9,98</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,54</t>
+          <t>3,93; 10,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,15</t>
+          <t>4,09; 9,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,22</t>
+          <t>4,66; 9,05</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,77; 21,35</t>
+          <t>10,2; 21,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 22,63</t>
+          <t>11,86; 23,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,36; 20,53</t>
+          <t>12,46; 20,38</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 19,51</t>
+          <t>6,73; 19,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 26,48</t>
+          <t>9,37; 25,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,74; 20,28</t>
+          <t>9,75; 20,67</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,07</t>
+          <t>6,98; 11,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 11,18</t>
+          <t>7,25; 11,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 10,52</t>
+          <t>7,67; 10,46</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3309; 12420</t>
+          <t>3607; 13650</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2308; 11116</t>
+          <t>2279; 12015</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7281; 20298</t>
+          <t>7623; 20204</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3880; 13324</t>
+          <t>3818; 12983</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2728; 11647</t>
+          <t>2906; 11865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7725; 20059</t>
+          <t>8015; 21232</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>812; 7158</t>
+          <t>906; 7609</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>896; 7255</t>
+          <t>796; 7369</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2791; 11657</t>
+          <t>2975; 11543</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8538; 22589</t>
+          <t>8427; 22395</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8484; 21580</t>
+          <t>8702; 21208</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19727; 39376</t>
+          <t>19906; 38622</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12339; 24449</t>
+          <t>11683; 24140</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18126; 35502</t>
+          <t>18599; 37629</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33553; 55718</t>
+          <t>33825; 55301</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4579; 12962</t>
+          <t>4474; 12955</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6323; 18243</t>
+          <t>6454; 17735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13176; 27445</t>
+          <t>13195; 27978</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44492; 71342</t>
+          <t>45024; 72807</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>52911; 81819</t>
+          <t>53027; 81570</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106080; 144737</t>
+          <t>105500; 143944</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$recibos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 13,27</t>
+          <t>2,23; 10,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,98</t>
+          <t>3,82; 13,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,53</t>
+          <t>3,62; 9,73</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 13,71</t>
+          <t>3,25; 13,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 12,41</t>
+          <t>3,64; 13,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 11,16</t>
+          <t>4,45; 11,11</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 14,67</t>
+          <t>1,59; 12,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,54</t>
+          <t>1,63; 15,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,98</t>
+          <t>2,25; 10,9</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,45</t>
+          <t>4,27; 10,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,97</t>
+          <t>5,15; 11,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,05</t>
+          <t>5,28; 10,04</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 21,08</t>
+          <t>12,4; 24,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 23,99</t>
+          <t>10,28; 21,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 20,38</t>
+          <t>13,06; 21,32</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,73; 19,5</t>
+          <t>9,93; 26,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 25,74</t>
+          <t>6,99; 19,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,75; 20,67</t>
+          <t>9,67; 20,56</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,98; 11,29</t>
+          <t>7,66; 11,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,15</t>
+          <t>7,81; 11,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,46</t>
+          <t>8,26; 11,12</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>13664</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3607; 13650</t>
+          <t>2672; 12056</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2279; 12015</t>
+          <t>3867; 13416</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7623; 20204</t>
+          <t>8009; 21506</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>13716</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3818; 12983</t>
+          <t>2968; 11978</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2906; 11865</t>
+          <t>3519; 12868</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8015; 21232</t>
+          <t>8362; 20889</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6224</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>906; 7609</t>
+          <t>906; 6893</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>796; 7369</t>
+          <t>874; 8077</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2975; 11543</t>
+          <t>2488; 12033</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28469</t>
+          <t>27619</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8427; 22395</t>
+          <t>8390; 20637</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8702; 21208</t>
+          <t>9057; 20865</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19906; 38622</t>
+          <t>19662; 37417</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17896</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>42898</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11683; 24140</t>
+          <t>17598; 34250</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18599; 37629</t>
+          <t>11716; 24756</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33825; 55301</t>
+          <t>33413; 54569</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>19556</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4474; 12955</t>
+          <t>6503; 17492</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6454; 17735</t>
+          <t>4755; 13086</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13195; 27978</t>
+          <t>12906; 27458</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>59304</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124393</t>
+          <t>123676</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45024; 72807</t>
+          <t>51466; 77916</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53027; 81570</t>
+          <t>47609; 72945</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>105500; 143944</t>
+          <t>105781; 142485</t>
         </is>
       </c>
     </row>
